--- a/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N60_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T6156_W0055F0002T0006Z000C1N60_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>23.69307771106596</v>
+        <v>3.850125128048219</v>
       </c>
       <c r="D2" t="n">
-        <v>50.87870368719008</v>
+        <v>8.267789349168387</v>
       </c>
       <c r="E2" t="n">
-        <v>10.85959388354551</v>
+        <v>1.764684006076145</v>
       </c>
       <c r="F2" t="n">
-        <v>13.0540869158908</v>
+        <v>2.121289123832254</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>15.4297945231872</v>
+        <v>2.50734161001792</v>
       </c>
       <c r="D3" t="n">
-        <v>15.45323554757671</v>
+        <v>2.511150776481216</v>
       </c>
       <c r="E3" t="n">
-        <v>10.85959388354551</v>
+        <v>1.764684006076145</v>
       </c>
       <c r="F3" t="n">
-        <v>13.0540869158908</v>
+        <v>2.121289123832254</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.07678976847943</v>
+        <v>3.912478337377908</v>
       </c>
       <c r="D4" t="n">
-        <v>39.21047721341063</v>
+        <v>6.371702547179227</v>
       </c>
       <c r="E4" t="n">
-        <v>10.85959388354551</v>
+        <v>1.764684006076145</v>
       </c>
       <c r="F4" t="n">
-        <v>13.0540869158908</v>
+        <v>2.121289123832254</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>39.12397357553387</v>
+        <v>6.357645706024254</v>
       </c>
       <c r="D5" t="n">
-        <v>39.35449508829617</v>
+        <v>6.395105451848128</v>
       </c>
       <c r="E5" t="n">
-        <v>10.85959388354551</v>
+        <v>1.764684006076145</v>
       </c>
       <c r="F5" t="n">
-        <v>13.0540869158908</v>
+        <v>2.121289123832254</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>44.86068754089538</v>
+        <v>7.289861725395499</v>
       </c>
       <c r="D6" t="n">
-        <v>51.51891178508625</v>
+        <v>8.371823165076517</v>
       </c>
       <c r="E6" t="n">
-        <v>10.85959388354551</v>
+        <v>1.764684006076145</v>
       </c>
       <c r="F6" t="n">
-        <v>13.0540869158908</v>
+        <v>2.121289123832254</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
